--- a/product_selector_out/STM32U3 series.xlsx
+++ b/product_selector_out/STM32U3 series.xlsx
@@ -5336,7 +5336,7 @@
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S25" s="4" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AD25" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="AE25" s="4" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S27" s="4" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AD27" s="4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>111, 114</t>
         </is>
       </c>
       <c r="AE27" s="4" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S28" s="4" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="AD28" s="4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>111, 114</t>
         </is>
       </c>
       <c r="AE28" s="4" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S29" s="4" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="AD29" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106, 110</t>
         </is>
       </c>
       <c r="AE29" s="4" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S30" s="4" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S31" s="4" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7625,7 +7625,7 @@
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S32" s="4" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="AD32" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE32" s="4" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7952,7 +7952,7 @@
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S33" s="4" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="AD33" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE33" s="4" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S34" s="4" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AD34" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE34" s="4" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S37" s="4" t="inlineStr">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9587,119 +9587,119 @@
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>Dual Watchdog, RTC, SysTick</t>
+        </is>
+      </c>
+      <c r="U38" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="W38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA38" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD38" s="4" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AE38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF38" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH38" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI38" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ38" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL38" s="4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T38" s="4" t="inlineStr">
-        <is>
-          <t>Dual Watchdog, RTC, SysTick</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr">
+      <c r="AM38" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V38" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="W38" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X38" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y38" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z38" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA38" s="4" t="inlineStr">
+      <c r="AN38" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB38" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC38" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD38" s="4" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AE38" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF38" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG38" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH38" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI38" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ38" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK38" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AL38" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM38" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN38" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AO38" s="4" t="inlineStr">
         <is>
           <t>ADF, SAI, SD/MMC</t>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="R39" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S39" s="4" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AD39" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106, 110</t>
         </is>
       </c>
       <c r="AE39" s="4" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10568,119 +10568,119 @@
       </c>
       <c r="R41" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T41" s="4" t="inlineStr">
+        <is>
+          <t>Dual Watchdog, RTC, SysTick</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="W41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA41" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD41" s="4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AE41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG41" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH41" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI41" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ41" s="4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T41" s="4" t="inlineStr">
-        <is>
-          <t>Dual Watchdog, RTC, SysTick</t>
-        </is>
-      </c>
-      <c r="U41" s="4" t="inlineStr">
+      <c r="AK41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL41" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM41" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V41" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="W41" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X41" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y41" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z41" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA41" s="4" t="inlineStr">
+      <c r="AN41" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB41" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC41" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD41" s="4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AE41" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF41" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG41" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH41" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI41" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ41" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK41" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AL41" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM41" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN41" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AO41" s="4" t="inlineStr">
         <is>
           <t>ADF, SAI, SD/MMC</t>
@@ -10803,7 +10803,7 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="R42" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S42" s="4" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="AD42" s="4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>111, 114</t>
         </is>
       </c>
       <c r="AE42" s="4" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="R43" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="S43" s="4" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="AD43" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106, 110</t>
         </is>
       </c>
       <c r="AE43" s="4" t="inlineStr">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11549,119 +11549,119 @@
       </c>
       <c r="R44" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>Dual Watchdog, RTC, SysTick</t>
+        </is>
+      </c>
+      <c r="U44" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="W44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA44" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD44" s="4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AE44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF44" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH44" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI44" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ44" s="4" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>Dual Watchdog, RTC, SysTick</t>
-        </is>
-      </c>
-      <c r="U44" s="4" t="inlineStr">
+      <c r="AK44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL44" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM44" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V44" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="W44" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X44" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y44" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z44" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA44" s="4" t="inlineStr">
+      <c r="AN44" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB44" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC44" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD44" s="4" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AE44" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF44" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AG44" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH44" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI44" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AJ44" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK44" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AL44" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM44" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN44" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AO44" s="4" t="inlineStr">
         <is>
           <t>ADF, SAI, SD/MMC</t>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12644,9 +12644,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY12" s="9" t="inlineStr">
@@ -12971,9 +12971,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY13" s="9" t="inlineStr">
@@ -13298,9 +13298,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY14" s="9" t="inlineStr">
@@ -13625,9 +13625,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY15" s="9" t="inlineStr">
@@ -13952,9 +13952,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY16" s="9" t="inlineStr">
@@ -14279,9 +14279,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY17" s="9" t="inlineStr">
@@ -14606,9 +14606,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY18" s="9" t="inlineStr">
@@ -14933,9 +14933,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY19" s="9" t="inlineStr">
@@ -15260,9 +15260,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY20" s="9" t="inlineStr">
@@ -15587,9 +15587,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY21" s="9" t="inlineStr">
@@ -15914,9 +15914,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY22" s="9" t="inlineStr">
@@ -16241,9 +16241,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY23" s="9" t="inlineStr">
@@ -16568,9 +16568,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY24" s="9" t="inlineStr">
@@ -16670,9 +16670,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -16735,19 +16735,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R25" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U25" s="6" t="inlineStr">
@@ -16795,9 +16795,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE25" s="8" t="inlineStr">
@@ -16835,9 +16835,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM25" s="6" t="inlineStr">
@@ -16890,24 +16890,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA25" s="6" t="inlineStr">
@@ -16970,9 +16970,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17222,9 +17222,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AY26" s="9" t="inlineStr">
@@ -17324,9 +17324,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
@@ -17389,19 +17389,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R27" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U27" s="6" t="inlineStr">
@@ -17449,9 +17449,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE27" s="8" t="inlineStr">
@@ -17489,9 +17489,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM27" s="6" t="inlineStr">
@@ -17544,24 +17544,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ27" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA27" s="6" t="inlineStr">
@@ -17624,9 +17624,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17651,9 +17651,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -17716,19 +17716,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R28" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U28" s="6" t="inlineStr">
@@ -17776,9 +17776,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE28" s="8" t="inlineStr">
@@ -17816,9 +17816,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM28" s="6" t="inlineStr">
@@ -17871,24 +17871,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ28" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA28" s="6" t="inlineStr">
@@ -17951,9 +17951,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17978,9 +17978,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -18043,19 +18043,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R29" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U29" s="6" t="inlineStr">
@@ -18103,9 +18103,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE29" s="8" t="inlineStr">
@@ -18143,9 +18143,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM29" s="6" t="inlineStr">
@@ -18198,24 +18198,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ29" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ29" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA29" s="6" t="inlineStr">
@@ -18278,9 +18278,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -18305,9 +18305,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -18370,19 +18370,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R30" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
@@ -18470,9 +18470,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM30" s="6" t="inlineStr">
@@ -18525,24 +18525,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ30" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA30" s="6" t="inlineStr">
@@ -18605,9 +18605,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -18632,9 +18632,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -18697,19 +18697,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R31" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U31" s="6" t="inlineStr">
@@ -18797,9 +18797,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM31" s="6" t="inlineStr">
@@ -18852,24 +18852,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ31" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA31" s="6" t="inlineStr">
@@ -18932,9 +18932,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -18959,9 +18959,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -19024,19 +19024,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R32" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U32" s="6" t="inlineStr">
@@ -19084,9 +19084,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE32" s="8" t="inlineStr">
@@ -19124,9 +19124,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM32" s="6" t="inlineStr">
@@ -19179,24 +19179,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ32" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA32" s="6" t="inlineStr">
@@ -19259,9 +19259,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -19286,9 +19286,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -19351,19 +19351,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R33" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U33" s="6" t="inlineStr">
@@ -19411,9 +19411,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE33" s="8" t="inlineStr">
@@ -19451,9 +19451,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM33" s="6" t="inlineStr">
@@ -19506,24 +19506,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA33" s="6" t="inlineStr">
@@ -19586,9 +19586,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -19613,9 +19613,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -19678,19 +19678,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R34" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U34" s="6" t="inlineStr">
@@ -19738,9 +19738,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE34" s="8" t="inlineStr">
@@ -19778,9 +19778,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM34" s="6" t="inlineStr">
@@ -19833,24 +19833,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA34" s="6" t="inlineStr">
@@ -19913,9 +19913,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -19940,9 +19940,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -20005,14 +20005,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T35" s="6" t="inlineStr">
@@ -20160,24 +20160,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ35" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ35" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA35" s="6" t="inlineStr">
@@ -20240,9 +20240,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -20267,9 +20267,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -20332,14 +20332,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T36" s="6" t="inlineStr">
@@ -20487,24 +20487,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA36" s="6" t="inlineStr">
@@ -20567,9 +20567,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -20594,9 +20594,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -20659,19 +20659,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R37" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U37" s="6" t="inlineStr">
@@ -20759,9 +20759,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM37" s="6" t="inlineStr">
@@ -20814,24 +20814,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA37" s="6" t="inlineStr">
@@ -20894,9 +20894,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -20921,9 +20921,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
@@ -20986,19 +20986,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R38" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="T38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U38" s="6" t="inlineStr">
@@ -21086,9 +21086,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM38" s="6" t="inlineStr">
@@ -21141,24 +21141,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ38" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA38" s="6" t="inlineStr">
@@ -21221,9 +21221,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21248,9 +21248,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -21313,19 +21313,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R39" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U39" s="6" t="inlineStr">
@@ -21373,9 +21373,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE39" s="8" t="inlineStr">
@@ -21413,9 +21413,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM39" s="6" t="inlineStr">
@@ -21468,24 +21468,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA39" s="6" t="inlineStr">
@@ -21548,9 +21548,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21575,9 +21575,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -21640,14 +21640,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T40" s="6" t="inlineStr">
@@ -21795,24 +21795,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA40" s="6" t="inlineStr">
@@ -21875,9 +21875,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21902,9 +21902,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -21967,19 +21967,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R41" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="T41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U41" s="6" t="inlineStr">
@@ -22067,9 +22067,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM41" s="6" t="inlineStr">
@@ -22122,24 +22122,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA41" s="6" t="inlineStr">
@@ -22202,9 +22202,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -22229,9 +22229,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -22294,19 +22294,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R42" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T42" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U42" s="6" t="inlineStr">
@@ -22354,9 +22354,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE42" s="8" t="inlineStr">
@@ -22394,9 +22394,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM42" s="6" t="inlineStr">
@@ -22449,24 +22449,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW42" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY42" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ42" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA42" s="6" t="inlineStr">
@@ -22529,9 +22529,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -22556,9 +22556,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -22621,19 +22621,19 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R43" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="T43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U43" s="6" t="inlineStr">
@@ -22681,9 +22681,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE43" s="8" t="inlineStr">
@@ -22721,9 +22721,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM43" s="6" t="inlineStr">
@@ -22776,24 +22776,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA43" s="6" t="inlineStr">
@@ -22856,9 +22856,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -22883,9 +22883,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -22948,19 +22948,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R44" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="T44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="S44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="T44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="U44" s="6" t="inlineStr">
@@ -23048,9 +23048,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM44" s="6" t="inlineStr">
@@ -23103,24 +23103,24 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AW44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AZ44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AZ44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BA44" s="6" t="inlineStr">
@@ -23183,9 +23183,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -23204,7 +23204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23297,7 +23297,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23309,7 +23309,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -23319,7 +23319,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
@@ -23331,7 +23331,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -23341,19 +23341,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32U385VG</t>
+          <t>STM32U385RG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
@@ -23375,7 +23375,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -23397,7 +23397,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -23407,7 +23407,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -23419,7 +23419,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -23429,7 +23429,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23441,7 +23441,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -23451,19 +23451,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32U385KG</t>
+          <t>STM32U385VG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -23473,19 +23473,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32U385KG</t>
+          <t>STM32U385VG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -23495,7 +23495,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
@@ -23507,7 +23507,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -23517,7 +23517,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -23529,7 +23529,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
+          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
@@ -23551,7 +23551,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -23561,19 +23561,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32U375KG</t>
+          <t>STM32U385KG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -23583,19 +23583,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32U375KG</t>
+          <t>STM32U385KG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -23605,19 +23605,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32U375KG</t>
+          <t>STM32U385KG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -23627,7 +23627,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
@@ -23639,7 +23639,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -23649,19 +23649,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32U375RG</t>
+          <t>STM32U375KG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -23671,19 +23671,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32U375RG</t>
+          <t>STM32U375KG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -23693,14 +23693,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32U375RG</t>
+          <t>STM32U375KG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -23722,7 +23722,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32U375RG</t>
+          <t>STM32U375KG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -23744,7 +23744,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -23766,7 +23766,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -23781,19 +23781,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -23803,19 +23803,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32U375KE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -23825,19 +23825,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375RG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -23847,19 +23847,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -23869,19 +23869,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -23891,19 +23891,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32U375CE</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -23913,19 +23913,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -23935,19 +23935,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375KE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -23957,19 +23957,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -23979,19 +23979,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -24001,19 +24001,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32U385CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -24023,19 +24023,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -24045,19 +24045,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U375CE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -24067,19 +24067,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -24089,19 +24089,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32U375CG</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -24111,19 +24111,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -24133,19 +24133,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -24155,14 +24155,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -24177,14 +24177,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .112</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32U375RE</t>
+          <t>STM32U385CG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -24206,7 +24206,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -24228,7 +24228,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -24243,19 +24243,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -24265,19 +24265,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32U375VE</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -24287,19 +24287,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375CG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -24309,19 +24309,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -24331,19 +24331,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -24353,19 +24353,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32U375VG</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -24375,19 +24375,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -24397,19 +24397,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U375RE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -24419,19 +24419,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -24441,19 +24441,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
+          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32U3B5CG</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -24463,19 +24463,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -24485,19 +24485,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -24507,19 +24507,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U375VE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -24529,19 +24529,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32U3B5CI</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -24551,19 +24551,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 1. STM32U375xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -24573,19 +24573,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -24595,14 +24595,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -24617,14 +24617,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .110</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32U3C5CI</t>
+          <t>STM32U375VG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -24646,7 +24646,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -24668,7 +24668,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -24683,19 +24683,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -24705,19 +24705,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32U3B5ZI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -24727,19 +24727,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3B5CG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -24749,19 +24749,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Other timer functions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -24771,19 +24771,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
+          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -24793,19 +24793,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
+          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32U3C5ZI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
+          <t>Supply Voltage (V) max</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -24815,19 +24815,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
+          <t>Table 27. General operating conditions: V_DD max varies by condition (3.6 (3.6); 2.7 (2.7)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Other timer functions</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -24837,19 +24837,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
+          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32U3C5QI</t>
+          <t>STM32U3C5CI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -24858,1436 +24858,6 @@
         </is>
       </c>
       <c r="D75" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>STM32U3C5QI</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>STM32U3C5QI</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>STM32U3B5WG</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>STM32U3B5WG</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>STM32U3B5WG</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>STM32U3B5WG</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>STM32U3C5WI</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>STM32U3C5WI</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>STM32U3C5WI</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>STM32U3C5WI</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>STM32U3B5RI</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>STM32U3B5RG</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>STM32U3C5RI</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>STM32U3B5VI</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>STM32U3B5VI</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>STM32U3B5VI</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>STM32U3B5VI</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>STM32U3B5VI</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>STM32U3C5VI</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>STM32U3C5VI</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>STM32U3C5VI</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>STM32U3C5VI</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>STM32U3C5VI</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>STM32U3B5WI</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>STM32U3B5WI</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>STM32U3B5WI</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>STM32U3B5WI</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>STM32U3C5JI</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3C5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>STM32U3C5JI</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>STM32U3C5JI</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . 121</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>STM32U3C5JI</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>STM32U3B5QI</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Table 12. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>STM32U3B5VG</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>STM32U3B5JI</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>STM32U3B5ZG</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>STM32U3B5QG</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Other timer functions</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Table 1. STM32U3B5xx features and peripheral counts decides RTC=Yes; ST also lists Dual Watchdog, SysTick, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>Table 27. General operating conditions: V_DD min reads '1.71(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,; Table 46. Current consumption during wake-up from Stop 1 mode on LDO. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .119</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>STM32U3B5JG</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (Run Mode (per MHz)) typ</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
         <is>
           <t>Table 31. Current consumption in Run mode on LDO, Coremark code with data processing running from flash memory,</t>
         </is>

--- a/product_selector_out/STM32U3 series.xlsx
+++ b/product_selector_out/STM32U3 series.xlsx
@@ -2453,7 +2453,7 @@
       </c>
       <c r="AD16" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE16" s="4" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AD18" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="AE18" s="4" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AD20" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="AE20" s="4" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="AD21" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE21" s="4" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="AD22" s="4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>79, 82</t>
         </is>
       </c>
       <c r="AE22" s="4" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="AD23" s="4" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>79, 82</t>
         </is>
       </c>
       <c r="AE23" s="4" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AD24" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="AE24" s="4" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AD25" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="AE25" s="4" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="AD26" s="4" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>33, 37</t>
         </is>
       </c>
       <c r="AE26" s="4" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AD27" s="4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>111, 114</t>
         </is>
       </c>
       <c r="AE27" s="4" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="AD28" s="4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>111, 114</t>
         </is>
       </c>
       <c r="AE28" s="4" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="AD29" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106, 110</t>
         </is>
       </c>
       <c r="AE29" s="4" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="AD31" s="4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AE31" s="4" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="AD32" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE32" s="4" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="AD33" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE33" s="4" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="AD34" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47, 51</t>
         </is>
       </c>
       <c r="AE34" s="4" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AD37" s="4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AE37" s="4" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AD38" s="4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE38" s="4" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AD39" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106, 110</t>
         </is>
       </c>
       <c r="AE39" s="4" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="AD41" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE41" s="4" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="AD42" s="4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>111, 114</t>
         </is>
       </c>
       <c r="AE42" s="4" t="inlineStr">
@@ -11282,7 +11282,7 @@
       </c>
       <c r="AD43" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>106, 110</t>
         </is>
       </c>
       <c r="AE43" s="4" t="inlineStr">
@@ -11609,7 +11609,7 @@
       </c>
       <c r="AD44" s="4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AE44" s="4" t="inlineStr">
@@ -13480,9 +13480,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
@@ -13807,9 +13807,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V16" s="6" t="inlineStr">
@@ -14134,9 +14134,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V17" s="6" t="inlineStr">
@@ -14461,9 +14461,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V18" s="6" t="inlineStr">
@@ -15115,9 +15115,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V20" s="6" t="inlineStr">
@@ -15442,9 +15442,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V21" s="6" t="inlineStr">
@@ -15769,9 +15769,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
@@ -16096,9 +16096,9 @@
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="U23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="V23" s="6" t="inlineStr">
@@ -18430,9 +18430,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE30" s="8" t="inlineStr">
@@ -18757,9 +18757,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE31" s="8" t="inlineStr">
@@ -20719,9 +20719,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE37" s="8" t="inlineStr">
@@ -21046,9 +21046,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE38" s="8" t="inlineStr">
@@ -22027,9 +22027,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE41" s="8" t="inlineStr">
@@ -23008,9 +23008,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AD44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AD44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AE44" s="8" t="inlineStr">

--- a/product_selector_out/STM32U3 series.xlsx
+++ b/product_selector_out/STM32U3 series.xlsx
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AM16" s="4" t="inlineStr">
         <is>
-          <t>1, 2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AN16" s="4" t="inlineStr">
@@ -13570,9 +13570,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN15" s="6" t="inlineStr">
@@ -13897,9 +13897,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN16" s="6" t="inlineStr">
@@ -14224,9 +14224,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN17" s="6" t="inlineStr">
@@ -14551,9 +14551,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN18" s="6" t="inlineStr">
@@ -15205,9 +15205,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN20" s="6" t="inlineStr">
@@ -15532,9 +15532,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN21" s="6" t="inlineStr">
@@ -15859,9 +15859,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN22" s="6" t="inlineStr">
@@ -16186,9 +16186,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN23" s="6" t="inlineStr">
@@ -16513,9 +16513,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN24" s="6" t="inlineStr">
@@ -16840,9 +16840,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN25" s="6" t="inlineStr">
@@ -17167,9 +17167,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN26" s="6" t="inlineStr">
@@ -17494,9 +17494,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN27" s="6" t="inlineStr">
@@ -17821,9 +17821,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN28" s="6" t="inlineStr">
@@ -18148,9 +18148,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN29" s="6" t="inlineStr">
@@ -18475,9 +18475,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN30" s="6" t="inlineStr">
@@ -18802,9 +18802,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN31" s="6" t="inlineStr">
@@ -19129,9 +19129,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN32" s="6" t="inlineStr">
@@ -19456,9 +19456,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN33" s="6" t="inlineStr">
@@ -19783,9 +19783,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN34" s="6" t="inlineStr">
@@ -20764,9 +20764,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN37" s="6" t="inlineStr">
@@ -21091,9 +21091,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN38" s="6" t="inlineStr">
@@ -21418,9 +21418,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN39" s="6" t="inlineStr">
@@ -22072,9 +22072,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN41" s="6" t="inlineStr">
@@ -22399,9 +22399,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN42" s="6" t="inlineStr">
@@ -22726,9 +22726,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN43" s="6" t="inlineStr">
@@ -23053,9 +23053,9 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AM44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AM44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AN44" s="6" t="inlineStr">

--- a/product_selector_out/STM32U3 series.xlsx
+++ b/product_selector_out/STM32U3 series.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM44"/>
+  <dimension ref="A1:BN44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.31640625" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u385cg.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u385cg.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u385cg.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u385cg.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u375ce.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -5898,6 +5975,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -6225,6 +6307,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -6552,6 +6639,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -6879,6 +6971,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -7206,6 +7303,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -7533,6 +7635,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -7860,6 +7967,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -8187,6 +8299,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -8514,6 +8631,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -8841,6 +8963,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -9168,6 +9295,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -9495,6 +9627,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -9822,6 +9959,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3c5ci.pdf</t>
         </is>
       </c>
@@ -10149,6 +10291,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -10476,6 +10623,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -10803,6 +10955,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -11130,6 +11287,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -11457,6 +11619,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
@@ -11784,12 +11951,17 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32u3b5cg.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -11810,16 +11982,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -11832,6 +12002,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -11851,7 +12022,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -11901,7 +12074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM44"/>
+  <dimension ref="A1:BN44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11969,6 +12142,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12302,6 +12476,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -12397,6 +12576,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -12719,7 +12899,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13046,7 +13231,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13373,7 +13563,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13700,7 +13895,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14027,7 +14227,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14354,7 +14559,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14681,7 +14891,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15008,7 +15223,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15335,7 +15555,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15662,7 +15887,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15989,7 +16219,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16316,7 +16551,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16643,7 +16883,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16970,7 +17215,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17297,7 +17547,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17624,7 +17879,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17951,7 +18211,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18278,7 +18543,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18605,7 +18875,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18932,7 +19207,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19259,7 +19539,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19586,7 +19871,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19913,7 +20203,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20240,7 +20535,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20567,7 +20867,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20894,7 +21199,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21221,7 +21531,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21548,7 +21863,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21875,7 +22195,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22202,7 +22527,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22529,7 +22859,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22856,7 +23191,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23183,7 +23523,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23191,8 +23536,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
